--- a/data/gas/processed/gas_to_power_reconciliation_2025H1.xlsx
+++ b/data/gas/processed/gas_to_power_reconciliation_2025H1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\thesis-code\data\gas\processed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\Thesis\thesis-repo\thesis-code\data\gas\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66976FB0-71A6-499D-9D1F-9489E9989A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E73703-E76D-499C-BFC0-D4CF7C6C378E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="96" windowWidth="15120" windowHeight="12132" xr2:uid="{41EBFF8F-819B-4B9E-BE44-3162811BFB4A}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{41EBFF8F-819B-4B9E-BE44-3162811BFB4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Period</t>
   </si>
@@ -39,16 +39,25 @@
     <t>thermal_generation_gwh</t>
   </si>
   <si>
-    <t>heating_value_btu_per_scf</t>
-  </si>
-  <si>
     <t>implied_efficiency</t>
   </si>
   <si>
     <t>notes</t>
   </si>
   <si>
-    <t>Thermal generation inferred from ‘energy billed’ table; total generation includes hydro and is excluded.”</t>
+    <t>Total Gas Energy (BTU)</t>
+  </si>
+  <si>
+    <t>Thermal generation inferred from ‘energy billed’ table; total generation includes hydro and is excluded.” 1kwh = 3412BTU</t>
+  </si>
+  <si>
+    <t>E.Energy Output</t>
+  </si>
+  <si>
+    <t>Nigeria Operates (as at 2025/Q4) 2 steam plants, 19 OCGT and 2 CCGT)</t>
+  </si>
+  <si>
+    <t>heating_value_btu_per_scf(HHV)</t>
   </si>
 </sst>
 </file>
@@ -92,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +113,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -420,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1DE5C9-8DC7-4ED9-BD7C-48F6B5B41F70}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -428,9 +440,11 @@
     <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,16 +455,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -463,11 +483,25 @@
       <c r="D2" s="4">
         <v>1036</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="5">
+        <f>G2/F2</f>
+        <v>0.43491420815192422</v>
+      </c>
+      <c r="F2" s="2">
+        <f>B2*10^6*D2</f>
+        <v>159418353920000</v>
+      </c>
+      <c r="G2" s="2">
+        <f>C2*10^6*3412</f>
+        <v>69333307160000</v>
+      </c>
+      <c r="H2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas/processed/gas_to_power_reconciliation_2025H1.xlsx
+++ b/data/gas/processed/gas_to_power_reconciliation_2025H1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\Thesis\thesis-repo\thesis-code\data\gas\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E73703-E76D-499C-BFC0-D4CF7C6C378E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096C1308-F07D-4BE9-A68B-4FDA2650C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{41EBFF8F-819B-4B9E-BE44-3162811BFB4A}"/>
+    <workbookView xWindow="10752" yWindow="0" windowWidth="11724" windowHeight="12228" xr2:uid="{41EBFF8F-819B-4B9E-BE44-3162811BFB4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Period</t>
   </si>
   <si>
-    <t>2025 (Q1-Q3)</t>
-  </si>
-  <si>
     <t>gas_to_power_mmscf</t>
   </si>
   <si>
@@ -58,6 +55,12 @@
   </si>
   <si>
     <t>heating_value_btu_per_scf(HHV)</t>
+  </si>
+  <si>
+    <t>gas_generation TWh_e</t>
+  </si>
+  <si>
+    <t>gas_to_power TWh_e</t>
   </si>
 </sst>
 </file>
@@ -432,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1DE5C9-8DC7-4ED9-BD7C-48F6B5B41F70}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -449,30 +452,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="2">
+        <v>2025</v>
       </c>
       <c r="B2" s="3">
         <v>153878.72</v>
@@ -496,12 +499,38 @@
         <v>69333307160000</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H3" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
